--- a/tools/_out/airway_first_20261020/stage/04_DESIGN_TABLES/DesignTable_6565.xlsx
+++ b/tools/_out/airway_first_20261020/stage/04_DESIGN_TABLES/DesignTable_6565.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:S11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +509,11 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -772,7 +777,12 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Air-Way s104 only (double-pass 9 rows); C3_1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!V2057 Nut Hex 1 = 1.000 (table had 0.94); C3_2HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!Y2057 Nut Hex 2 = 1.000 (table had 0.94) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>[BRENNAN-CELL 2026-10-20: C3_2HEX@HEX] [BRENNAN-CELL 2026-10-20: C3_1HEX@HEX] Air-Way s104 only (double-pass 9 rows); C3_1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!V2057 Nut Hex 1 = 1.000 (table had 0.94); C3_2HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!Y2057 Nut Hex 2 = 1.000 (table had 0.94) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C3_1HEX@HEX: Brennan TFA catalog p18 table TFA-p018-t04 "FJS-FJS STRAIGHT" row 6565-10-10 col "C1 HEX" = 1.000 [user 2026-10-20 Q1: Air-Way value cannot be built -&gt; Brennan]; C3_2HEX@HEX: Brennan TFA catalog p18 table TFA-p018-t04 "FJS-FJS STRAIGHT" row 6565-10-10 col "C2 HEX" = 1.000 [user 2026-10-20 Q1: Air-Way value cannot be built -&gt; Brennan]</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2026-10-20 C3_1HEX@HEX = Brennan 1 (Air-Way 0.94 cannot be built: Air-Way nut hex 0.94 vs the Brennan -10 swivel nut (1.000) the nut shape is measured from (generator: no end data)) | 2026-10-20 C3_2HEX@HEX = Brennan 1 (Air-Way 0.94 cannot be built: Air-Way nut hex 0.94 vs the Brennan -10 swivel nut (1.000) the nut shape is measured from (generator: no end data))</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -783,6 +793,11 @@
       <c r="R6" t="inlineStr">
         <is>
           <t>6565-10-10</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
